--- a/output/pdf_financials_xlsx/GRA.xlsx
+++ b/output/pdf_financials_xlsx/GRA.xlsx
@@ -4315,28 +4315,28 @@
         <v>0</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>0.01349</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>0.012927</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>0.058505</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>0.088173</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>0.01207</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>0.034552</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>-0.1629</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>0.095323</v>
       </c>
     </row>
     <row r="92">
@@ -4365,10 +4365,10 @@
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.588215</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.880555</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>0</v>
@@ -8040,7 +8040,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -10970,7 +10974,11 @@
           <t>Reserve</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -13403,7 +13411,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -14596,7 +14608,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GRA.xlsx
+++ b/output/pdf_financials_xlsx/GRA.xlsx
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.421214</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>15.268666</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>27.81914</v>
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.421214</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>15.268666</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>27.81914</v>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.212725</v>
+        <v>0.791511</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>20.034607</v>
+        <v>4.765941</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>23.473249</v>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">

--- a/output/pdf_financials_xlsx/GRA.xlsx
+++ b/output/pdf_financials_xlsx/GRA.xlsx
@@ -16506,7 +16506,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
